--- a/Shadow_Rate.xlsx
+++ b/Shadow_Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timjascheck/Documents/GitHub/Quaterly-Output-Gap/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anatos91\Documents\Quaterly-Output-Gap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9572A14C-A77B-C14E-AE60-5661850006AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5F7371-04F8-4960-9760-FB7CFAB3BC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27800" windowHeight="17500" xr2:uid="{0213BDFE-3621-E344-BD93-79FCE972E175}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0213BDFE-3621-E344-BD93-79FCE972E175}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -93,9 +93,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -133,7 +133,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -239,7 +239,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -381,7 +381,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -390,12 +390,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4713B6-CA3D-7946-85A2-3C1E3D93275A}">
   <dimension ref="A1:B217"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="256" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="29.8984375" customWidth="1"/>
+    <col min="2" max="256" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -403,7 +404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>200409</v>
       </c>
@@ -411,7 +412,7 @@
         <v>2.0447360085182495</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>200410</v>
       </c>
@@ -419,7 +420,7 @@
         <v>2.1357639484303625</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>200411</v>
       </c>
@@ -427,7 +428,7 @@
         <v>2.1681051712676265</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>200412</v>
       </c>
@@ -435,7 +436,7 @@
         <v>2.075329865487884</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>200501</v>
       </c>
@@ -443,7 +444,7 @@
         <v>2.0284758003161514</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>200502</v>
       </c>
@@ -451,7 +452,7 @@
         <v>1.9874598327592281</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>200503</v>
       </c>
@@ -459,7 +460,7 @@
         <v>2.0028966008252311</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>200504</v>
       </c>
@@ -467,7 +468,7 @@
         <v>2.053499619416904</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>200505</v>
       </c>
@@ -475,7 +476,7 @@
         <v>2.0857671407800176</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>200506</v>
       </c>
@@ -483,7 +484,7 @@
         <v>2.1122235601383075</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>200507</v>
       </c>
@@ -491,7 +492,7 @@
         <v>2.1170651790874437</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>200508</v>
       </c>
@@ -499,7 +500,7 @@
         <v>2.1022686282910676</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>200509</v>
       </c>
@@ -507,7 +508,7 @@
         <v>1.9800761063536783</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>200510</v>
       </c>
@@ -515,7 +516,7 @@
         <v>2.1470197336138206</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>200511</v>
       </c>
@@ -523,7 +524,7 @@
         <v>2.3497015324925989</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>200512</v>
       </c>
@@ -531,7 +532,7 @@
         <v>2.3013087956474436</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>200601</v>
       </c>
@@ -539,7 +540,7 @@
         <v>2.2861926129106074</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>200602</v>
       </c>
@@ -547,7 +548,7 @@
         <v>2.3231834065523316</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>200603</v>
       </c>
@@ -555,7 +556,7 @@
         <v>2.5180253092168563</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>200604</v>
       </c>
@@ -563,7 +564,7 @@
         <v>2.5445335318251985</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>200605</v>
       </c>
@@ -571,7 +572,7 @@
         <v>2.7401602552055166</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>200606</v>
       </c>
@@ -579,7 +580,7 @@
         <v>2.8227288346357184</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>200607</v>
       </c>
@@ -587,7 +588,7 @@
         <v>2.981374375174024</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>200608</v>
       </c>
@@ -595,7 +596,7 @@
         <v>3.2144115705142404</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>200609</v>
       </c>
@@ -603,7 +604,7 @@
         <v>3.3606117950744796</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>200610</v>
       </c>
@@ -611,7 +612,7 @@
         <v>3.3911580650094706</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>200611</v>
       </c>
@@ -619,7 +620,7 @@
         <v>3.4241428126961964</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>200612</v>
       </c>
@@ -627,7 +628,7 @@
         <v>3.4797052155116077</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>200701</v>
       </c>
@@ -635,7 +636,7 @@
         <v>3.5605909860600811</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>200702</v>
       </c>
@@ -643,7 +644,7 @@
         <v>3.6190706133228296</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>200703</v>
       </c>
@@ -651,7 +652,7 @@
         <v>3.7235367731878029</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>200704</v>
       </c>
@@ -659,7 +660,7 @@
         <v>3.7510659335054832</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>200705</v>
       </c>
@@ -667,7 +668,7 @@
         <v>3.8500335445764193</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>200706</v>
       </c>
@@ -675,7 +676,7 @@
         <v>3.9105303913460219</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>200707</v>
       </c>
@@ -683,7 +684,7 @@
         <v>4.006874899685144</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>200708</v>
       </c>
@@ -691,7 +692,7 @@
         <v>3.816323646883319</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>200709</v>
       </c>
@@ -699,7 +700,7 @@
         <v>3.763280873974189</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>200710</v>
       </c>
@@ -707,7 +708,7 @@
         <v>3.8477540965943327</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>200711</v>
       </c>
@@ -715,7 +716,7 @@
         <v>3.8837958045829701</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>200712</v>
       </c>
@@ -723,7 +724,7 @@
         <v>3.9645311978558482</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>200801</v>
       </c>
@@ -731,7 +732,7 @@
         <v>3.8766999786310592</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>200802</v>
       </c>
@@ -739,7 +740,7 @@
         <v>4.0531119752918698</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>200803</v>
       </c>
@@ -747,7 +748,7 @@
         <v>4.0122059973904811</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>200804</v>
       </c>
@@ -755,7 +756,7 @@
         <v>4.0245527393552933</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>200805</v>
       </c>
@@ -763,7 +764,7 @@
         <v>4.0466892540548578</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>200806</v>
       </c>
@@ -771,7 +772,7 @@
         <v>4.1591700892583745</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>200807</v>
       </c>
@@ -779,7 +780,7 @@
         <v>4.2491324977170422</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>200808</v>
       </c>
@@ -787,7 +788,7 @@
         <v>4.278509906524107</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>200809</v>
       </c>
@@ -795,7 +796,7 @@
         <v>3.7536965613845297</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>200810</v>
       </c>
@@ -803,7 +804,7 @@
         <v>4.2582111646957799</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>200811</v>
       </c>
@@ -811,7 +812,7 @@
         <v>1.9333336905544058</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>200812</v>
       </c>
@@ -819,7 +820,7 @@
         <v>1.6249197737223717</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>200901</v>
       </c>
@@ -827,7 +828,7 @@
         <v>0.79728150213549398</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>200902</v>
       </c>
@@ -835,7 +836,7 @@
         <v>0.4098093094114077</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>200903</v>
       </c>
@@ -843,7 +844,7 @@
         <v>0.1239949559832354</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>200904</v>
       </c>
@@ -851,7 +852,7 @@
         <v>0.27518214998302781</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>200905</v>
       </c>
@@ -859,7 +860,7 @@
         <v>0.26616518853025539</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>200906</v>
       </c>
@@ -867,7 +868,7 @@
         <v>0.17148082400548503</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>200907</v>
       </c>
@@ -875,7 +876,7 @@
         <v>-0.46495675046440965</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>200908</v>
       </c>
@@ -883,7 +884,7 @@
         <v>-0.73042014237093511</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>200909</v>
       </c>
@@ -891,7 +892,7 @@
         <v>-0.42021012226872045</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>200910</v>
       </c>
@@ -899,7 +900,7 @@
         <v>-0.1190910389061699</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>200911</v>
       </c>
@@ -907,7 +908,7 @@
         <v>0.13401279979658298</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>200912</v>
       </c>
@@ -915,7 +916,7 @@
         <v>0.19245778726226348</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>201001</v>
       </c>
@@ -923,7 +924,7 @@
         <v>0.1889799920733779</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>201002</v>
       </c>
@@ -931,7 +932,7 @@
         <v>2.9355690485935781E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>201003</v>
       </c>
@@ -939,7 +940,7 @@
         <v>0.2122224652154614</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>201004</v>
       </c>
@@ -947,7 +948,7 @@
         <v>0.33620301904010219</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>201005</v>
       </c>
@@ -955,7 +956,7 @@
         <v>4.6410158089461362E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>201006</v>
       </c>
@@ -963,7 +964,7 @@
         <v>0.39749030405291563</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>201007</v>
       </c>
@@ -971,7 +972,7 @@
         <v>0.6417872583047135</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>201008</v>
       </c>
@@ -979,7 +980,7 @@
         <v>0.5351801356352972</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>201009</v>
       </c>
@@ -987,7 +988,7 @@
         <v>0.80436674259452445</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>201010</v>
       </c>
@@ -995,7 +996,7 @@
         <v>0.95931608565143733</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>201011</v>
       </c>
@@ -1003,7 +1004,7 @@
         <v>0.76461595977075447</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>201012</v>
       </c>
@@ -1011,7 +1012,7 @@
         <v>0.52188641051786533</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>201101</v>
       </c>
@@ -1019,7 +1020,7 @@
         <v>0.67846314502103056</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>201102</v>
       </c>
@@ -1027,7 +1028,7 @@
         <v>0.6363800553965504</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>201103</v>
       </c>
@@ -1035,7 +1036,7 @@
         <v>0.71147068803819735</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>201104</v>
       </c>
@@ -1043,7 +1044,7 @@
         <v>0.85814951620882951</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>201105</v>
       </c>
@@ -1051,7 +1052,7 @@
         <v>1.0304552420715538</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>201106</v>
       </c>
@@ -1059,7 +1060,7 @@
         <v>1.3402960945844136</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>201107</v>
       </c>
@@ -1067,7 +1068,7 @@
         <v>1.2645526956928244</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>201108</v>
       </c>
@@ -1075,7 +1076,7 @@
         <v>0.96240578836226831</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>201109</v>
       </c>
@@ -1083,7 +1084,7 @@
         <v>0.40539584377820148</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>201110</v>
       </c>
@@ -1091,7 +1092,7 @@
         <v>0.5788928501106696</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>201111</v>
       </c>
@@ -1099,7 +1100,7 @@
         <v>6.6368513426489528E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>201112</v>
       </c>
@@ -1107,7 +1108,7 @@
         <v>-0.73267994104638845</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>201201</v>
       </c>
@@ -1115,7 +1116,7 @@
         <v>-0.29504716160528943</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>201202</v>
       </c>
@@ -1123,7 +1124,7 @@
         <v>-0.46677923883563111</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>201203</v>
       </c>
@@ -1131,7 +1132,7 @@
         <v>-0.21804300215102757</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>201204</v>
       </c>
@@ -1139,7 +1140,7 @@
         <v>-0.40326812229043085</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>201205</v>
       </c>
@@ -1147,7 +1148,7 @@
         <v>-0.92081757165927769</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>201206</v>
       </c>
@@ -1155,7 +1156,7 @@
         <v>-0.67433711381395511</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>201207</v>
       </c>
@@ -1163,7 +1164,7 @@
         <v>-0.94125856160480836</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>201208</v>
       </c>
@@ -1171,7 +1172,7 @@
         <v>-1.0773140459555819</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>201209</v>
       </c>
@@ -1179,7 +1180,7 @@
         <v>-1.0113929082731516</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>201210</v>
       </c>
@@ -1187,7 +1188,7 @@
         <v>-0.93299900569295957</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>201211</v>
       </c>
@@ -1195,7 +1196,7 @@
         <v>-0.9804780444587351</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>201212</v>
       </c>
@@ -1203,7 +1204,7 @@
         <v>-1.0864902001155414</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>201301</v>
       </c>
@@ -1211,7 +1212,7 @@
         <v>-0.60739545580533516</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>201302</v>
       </c>
@@ -1219,7 +1220,7 @@
         <v>-0.80991124885519739</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>201303</v>
       </c>
@@ -1227,7 +1228,7 @@
         <v>-0.62494092795404299</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>201304</v>
       </c>
@@ -1235,7 +1236,7 @@
         <v>-0.67510285781694179</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>201305</v>
       </c>
@@ -1243,7 +1244,7 @@
         <v>-0.17957448799104725</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>201306</v>
       </c>
@@ -1251,7 +1252,7 @@
         <v>0.5192132110007428</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A108">
         <v>201307</v>
       </c>
@@ -1259,7 +1260,7 @@
         <v>-0.41819594425337669</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A109">
         <v>201308</v>
       </c>
@@ -1267,7 +1268,7 @@
         <v>-0.22300949247244262</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A110">
         <v>201309</v>
       </c>
@@ -1275,7 +1276,7 @@
         <v>-0.40967663059078063</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A111">
         <v>201310</v>
       </c>
@@ -1283,7 +1284,7 @@
         <v>-0.37846022432680115</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A112">
         <v>201311</v>
       </c>
@@ -1291,7 +1292,7 @@
         <v>-0.28997235602304983</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A113">
         <v>201312</v>
       </c>
@@ -1299,7 +1300,7 @@
         <v>-0.118251928921012</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A114">
         <v>201401</v>
       </c>
@@ -1307,7 +1308,7 @@
         <v>-0.49043188830192008</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115">
         <v>201402</v>
       </c>
@@ -1315,7 +1316,7 @@
         <v>-0.60148335818003318</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116">
         <v>201403</v>
       </c>
@@ -1323,7 +1324,7 @@
         <v>-0.69596967373156104</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117">
         <v>201404</v>
       </c>
@@ -1331,7 +1332,7 @@
         <v>-0.73401956944633895</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118">
         <v>201405</v>
       </c>
@@ -1339,7 +1340,7 @@
         <v>-0.82404626192146324</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A119">
         <v>201406</v>
       </c>
@@ -1347,7 +1348,7 @@
         <v>-0.86085107914514936</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120">
         <v>201407</v>
       </c>
@@ -1355,7 +1356,7 @@
         <v>-0.95766362463290022</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121">
         <v>201408</v>
       </c>
@@ -1363,7 +1364,7 @@
         <v>-1.33886736574037</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122">
         <v>201409</v>
       </c>
@@ -1371,7 +1372,7 @@
         <v>-1.3321349772162989</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123">
         <v>201410</v>
       </c>
@@ -1379,7 +1380,7 @@
         <v>-1.5501118658917896</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124">
         <v>201411</v>
       </c>
@@ -1387,7 +1388,7 @@
         <v>-1.8859676474958107</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125">
         <v>201412</v>
       </c>
@@ -1395,7 +1396,7 @@
         <v>-2.2490178627318116</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126">
         <v>201501</v>
       </c>
@@ -1403,7 +1404,7 @@
         <v>-2.6314613569321779</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127">
         <v>201502</v>
       </c>
@@ -1411,7 +1412,7 @@
         <v>-2.5611940144095442</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128">
         <v>201503</v>
       </c>
@@ -1419,7 +1420,7 @@
         <v>-2.596925684678979</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A129">
         <v>201504</v>
       </c>
@@ -1427,7 +1428,7 @@
         <v>-2.0041766614171479</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A130">
         <v>201505</v>
       </c>
@@ -1435,7 +1436,7 @@
         <v>-2.3478588781342751</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A131">
         <v>201506</v>
       </c>
@@ -1443,7 +1444,7 @@
         <v>-2.3401699310248176</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A132">
         <v>201507</v>
       </c>
@@ -1451,7 +1452,7 @@
         <v>-2.5641836245170602</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A133">
         <v>201508</v>
       </c>
@@ -1459,7 +1460,7 @@
         <v>-2.4012604500752168</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A134">
         <v>201509</v>
       </c>
@@ -1467,7 +1468,7 @@
         <v>-2.5592600530659411</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A135">
         <v>201510</v>
       </c>
@@ -1475,7 +1476,7 @@
         <v>-2.7291915410364069</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A136">
         <v>201511</v>
       </c>
@@ -1483,7 +1484,7 @@
         <v>-2.8605613593549464</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A137">
         <v>201512</v>
       </c>
@@ -1491,7 +1492,7 @@
         <v>-2.5615593804251624</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A138">
         <v>201601</v>
       </c>
@@ -1499,7 +1500,7 @@
         <v>-3.2217375466372644</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A139">
         <v>201602</v>
       </c>
@@ -1507,7 +1508,7 @@
         <v>-3.6768847664501436</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A140">
         <v>201603</v>
       </c>
@@ -1515,7 +1516,7 @@
         <v>-3.7627687021640703</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A141">
         <v>201604</v>
       </c>
@@ -1523,7 +1524,7 @@
         <v>-3.6241149816973248</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A142">
         <v>201605</v>
       </c>
@@ -1531,7 +1532,7 @@
         <v>-3.8114574629754294</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A143">
         <v>201606</v>
       </c>
@@ -1539,7 +1540,7 @@
         <v>-4.3353955030014291</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A144">
         <v>201607</v>
       </c>
@@ -1547,7 +1548,7 @@
         <v>-4.5447530977606299</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A145">
         <v>201608</v>
       </c>
@@ -1555,7 +1556,7 @@
         <v>-4.5219488062080764</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A146">
         <v>201609</v>
       </c>
@@ -1563,7 +1564,7 @@
         <v>-4.569582325299816</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A147">
         <v>201610</v>
       </c>
@@ -1571,7 +1572,7 @@
         <v>-3.6245081853307113</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A148">
         <v>201611</v>
       </c>
@@ -1579,7 +1580,7 @@
         <v>-4.1779164831309679</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A149">
         <v>201612</v>
       </c>
@@ -1587,7 +1588,7 @@
         <v>-4.5237854500933778</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A150">
         <v>201701</v>
       </c>
@@ -1595,7 +1596,7 @@
         <v>-4.6239296591385504</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A151">
         <v>201702</v>
       </c>
@@ -1603,7 +1604,7 @@
         <v>-5.3222699917203364</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A152">
         <v>201703</v>
       </c>
@@ -1611,7 +1612,7 @@
         <v>-5.3752556554153053</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A153">
         <v>201704</v>
       </c>
@@ -1619,7 +1620,7 @@
         <v>-5.3340768930915168</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A154">
         <v>201705</v>
       </c>
@@ -1627,7 +1628,7 @@
         <v>-5.5020419040950479</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A155">
         <v>201706</v>
       </c>
@@ -1635,7 +1636,7 @@
         <v>-5.1359423212059667</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A156">
         <v>201707</v>
       </c>
@@ -1643,7 +1644,7 @@
         <v>-5.1847684131380767</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A157">
         <v>201708</v>
       </c>
@@ -1651,7 +1652,7 @@
         <v>-5.4388435297173743</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A158">
         <v>201709</v>
       </c>
@@ -1659,7 +1660,7 @@
         <v>-5.2563992993764828</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A159">
         <v>201710</v>
       </c>
@@ -1667,7 +1668,7 @@
         <v>-5.3181067240415096</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A160">
         <v>201711</v>
       </c>
@@ -1675,7 +1676,7 @@
         <v>-5.2229649454332261</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A161">
         <v>201712</v>
       </c>
@@ -1683,7 +1684,7 @@
         <v>-4.8251996323996913</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A162">
         <v>201801</v>
       </c>
@@ -1691,7 +1692,7 @@
         <v>-4.7182999963406154</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A163">
         <v>201802</v>
       </c>
@@ -1699,7 +1700,7 @@
         <v>-5.1466281927465083</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A164">
         <v>201803</v>
       </c>
@@ -1707,7 +1708,7 @@
         <v>-5.476130644951084</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A165">
         <v>201804</v>
       </c>
@@ -1715,7 +1716,7 @@
         <v>-5.5954838078023563</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A166">
         <v>201805</v>
       </c>
@@ -1723,7 +1724,7 @@
         <v>-6.1347754267189316</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A167">
         <v>201806</v>
       </c>
@@ -1731,7 +1732,7 @@
         <v>-6.3408536067765766</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A168">
         <v>201807</v>
       </c>
@@ -1739,7 +1740,7 @@
         <v>-6.290156486753979</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A169">
         <v>201808</v>
       </c>
@@ -1747,7 +1748,7 @@
         <v>-6.4017240568044862</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A170">
         <v>201809</v>
       </c>
@@ -1755,7 +1756,7 @@
         <v>-6.2217762499506577</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A171">
         <v>201810</v>
       </c>
@@ -1763,7 +1764,7 @@
         <v>-6.1745006076335471</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A172">
         <v>201811</v>
       </c>
@@ -1771,7 +1772,7 @@
         <v>-6.2358680672826488</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A173">
         <v>201812</v>
       </c>
@@ -1779,7 +1780,7 @@
         <v>-6.1542950730872086</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A174">
         <v>201901</v>
       </c>
@@ -1787,7 +1788,7 @@
         <v>-6.3397520540315355</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A175">
         <v>201902</v>
       </c>
@@ -1795,7 +1796,7 @@
         <v>-6.2922112026096002</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A176">
         <v>201903</v>
       </c>
@@ -1803,7 +1804,7 @@
         <v>-6.6025924038364359</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A177">
         <v>201904</v>
       </c>
@@ -1811,7 +1812,7 @@
         <v>-6.4430546716659265</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A178">
         <v>201905</v>
       </c>
@@ -1819,7 +1820,7 @@
         <v>-6.8278500739190946</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A179">
         <v>201906</v>
       </c>
@@ -1827,7 +1828,7 @@
         <v>-7.0868538064667277</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A180">
         <v>201907</v>
       </c>
@@ -1835,7 +1836,7 @@
         <v>-7.3432012195563843</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A181">
         <v>201908</v>
       </c>
@@ -1843,7 +1844,7 @@
         <v>-7.8236187391893921</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A182">
         <v>201909</v>
       </c>
@@ -1851,7 +1852,7 @@
         <v>-7.7197321937464061</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A183">
         <v>201910</v>
       </c>
@@ -1859,7 +1860,7 @@
         <v>-7.4186361046874261</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A184">
         <v>201911</v>
       </c>
@@ -1867,7 +1868,7 @@
         <v>-7.174650937981049</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A185">
         <v>201912</v>
       </c>
@@ -1875,7 +1876,7 @@
         <v>-6.403677481852263</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A186">
         <v>202001</v>
       </c>
@@ -1883,7 +1884,7 @@
         <v>-6.9129495363079876</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A187">
         <v>202002</v>
       </c>
@@ -1891,7 +1892,7 @@
         <v>-7.3391611666020928</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A188">
         <v>202003</v>
       </c>
@@ -1899,7 +1900,7 @@
         <v>-6.9994446459975563</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A189">
         <v>202004</v>
       </c>
@@ -1907,7 +1908,7 @@
         <v>-7.2735035501309042</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A190">
         <v>202005</v>
       </c>
@@ -1915,7 +1916,7 @@
         <v>-7.1414966469114844</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A191">
         <v>202006</v>
       </c>
@@ -1923,7 +1924,7 @@
         <v>-7.3616247973633264</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A192">
         <v>202007</v>
       </c>
@@ -1931,7 +1932,7 @@
         <v>-7.5352512653699542</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A193">
         <v>202008</v>
       </c>
@@ -1939,7 +1940,7 @@
         <v>-7.180281195470446</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A194">
         <v>202009</v>
       </c>
@@ -1947,7 +1948,7 @@
         <v>-7.6237377100525201</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A195">
         <v>202010</v>
       </c>
@@ -1955,7 +1956,7 @@
         <v>-7.8072643261338683</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A196">
         <v>202011</v>
       </c>
@@ -1963,7 +1964,7 @@
         <v>-7.7263810928499126</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A197">
         <v>202012</v>
       </c>
@@ -1971,7 +1972,7 @@
         <v>-7.6827672026587841</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A198">
         <v>202101</v>
       </c>
@@ -1979,7 +1980,7 @@
         <v>-7.3520940044368857</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A199">
         <v>202102</v>
       </c>
@@ -1987,7 +1988,7 @@
         <v>-6.2337768820148867</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A200">
         <v>202103</v>
       </c>
@@ -1995,7 +1996,7 @@
         <v>-6.3829108361952862</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A201">
         <v>202104</v>
       </c>
@@ -2003,7 +2004,7 @@
         <v>-6.135400993420955</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A202">
         <v>202105</v>
       </c>
@@ -2011,7 +2012,7 @@
         <v>-6.0375990976551108</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A203">
         <v>202106</v>
       </c>
@@ -2019,7 +2020,7 @@
         <v>-6.0575965713214579</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A204">
         <v>202107</v>
       </c>
@@ -2027,7 +2028,7 @@
         <v>-6.6647783010910331</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A205">
         <v>202108</v>
       </c>
@@ -2035,7 +2036,7 @@
         <v>-6.6399121054323977</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A206">
         <v>202109</v>
       </c>
@@ -2043,7 +2044,7 @@
         <v>-5.8174588058182977</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A207">
         <v>202110</v>
       </c>
@@ -2051,7 +2052,7 @@
         <v>-4.774694731450289</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A208">
         <v>202111</v>
       </c>
@@ -2059,7 +2060,7 @@
         <v>-5.3605316448734435</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A209">
         <v>202112</v>
       </c>
@@ -2067,7 +2068,7 @@
         <v>-5.2645946567740296</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A210">
         <v>202201</v>
       </c>
@@ -2075,7 +2076,7 @@
         <v>-5.0069919724825418</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A211">
         <v>202202</v>
       </c>
@@ -2083,7 +2084,7 @@
         <v>-5.2879082119898371</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A212">
         <v>202203</v>
       </c>
@@ -2091,7 +2092,7 @@
         <v>-4.1316344681484409</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A213">
         <v>202204</v>
       </c>
@@ -2099,7 +2100,7 @@
         <v>-3.5517215120672461</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A214">
         <v>202205</v>
       </c>
@@ -2107,7 +2108,7 @@
         <v>-3.0786801554643191</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A215">
         <v>202206</v>
       </c>
@@ -2115,7 +2116,7 @@
         <v>-0.94917831600935187</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A216">
         <v>202207</v>
       </c>
@@ -2123,7 +2124,7 @@
         <v>-1.5786254054644004</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A217">
         <v>202208</v>
       </c>
